--- a/artfynd/A 51794-2019 artfynd.xlsx
+++ b/artfynd/A 51794-2019 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119854126</v>
+        <v>119854067</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,28 +798,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463088</v>
+        <v>462894</v>
       </c>
       <c r="R3" t="n">
-        <v>6718968</v>
+        <v>6718746</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119854067</v>
+        <v>119854126</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,26 +904,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462894</v>
+        <v>463088</v>
       </c>
       <c r="R4" t="n">
-        <v>6718746</v>
+        <v>6718968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 51794-2019 artfynd.xlsx
+++ b/artfynd/A 51794-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119854075</v>
+        <v>119854067</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462904</v>
+        <v>462894</v>
       </c>
       <c r="R2" t="n">
-        <v>6718824</v>
+        <v>6718746</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119854067</v>
+        <v>119854098</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462894</v>
+        <v>462896</v>
       </c>
       <c r="R3" t="n">
-        <v>6718746</v>
+        <v>6718825</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -996,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119854098</v>
+        <v>119854075</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,30 +1007,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462896</v>
+        <v>462904</v>
       </c>
       <c r="R5" t="n">
-        <v>6718825</v>
+        <v>6718824</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 51794-2019 artfynd.xlsx
+++ b/artfynd/A 51794-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119854098</v>
+        <v>119854126</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462896</v>
+        <v>463088</v>
       </c>
       <c r="R3" t="n">
-        <v>6718825</v>
+        <v>6718968</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119854126</v>
+        <v>119854075</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,32 +901,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463088</v>
+        <v>462904</v>
       </c>
       <c r="R4" t="n">
-        <v>6718968</v>
+        <v>6718824</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119854075</v>
+        <v>119854098</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,31 +1008,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462904</v>
+        <v>462896</v>
       </c>
       <c r="R5" t="n">
-        <v>6718824</v>
+        <v>6718825</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 51794-2019 artfynd.xlsx
+++ b/artfynd/A 51794-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119854067</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119854126</v>
+        <v>119854075</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,32 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463088</v>
+        <v>462904</v>
       </c>
       <c r="R3" t="n">
-        <v>6718968</v>
+        <v>6718824</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119854075</v>
+        <v>119854126</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,31 +900,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462904</v>
+        <v>463088</v>
       </c>
       <c r="R4" t="n">
-        <v>6718824</v>
+        <v>6718968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,7 +999,7 @@
         <v>119854098</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51794-2019 artfynd.xlsx
+++ b/artfynd/A 51794-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119854067</v>
+        <v>119854126</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462894</v>
+        <v>463088</v>
       </c>
       <c r="R2" t="n">
-        <v>6718746</v>
+        <v>6718968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119854075</v>
+        <v>119854098</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +795,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462904</v>
+        <v>462896</v>
       </c>
       <c r="R3" t="n">
-        <v>6718824</v>
+        <v>6718825</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119854126</v>
+        <v>119854075</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,32 +901,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463088</v>
+        <v>462904</v>
       </c>
       <c r="R4" t="n">
-        <v>6718968</v>
+        <v>6718824</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119854098</v>
+        <v>119854067</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462896</v>
+        <v>462894</v>
       </c>
       <c r="R5" t="n">
-        <v>6718825</v>
+        <v>6718746</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 51794-2019 artfynd.xlsx
+++ b/artfynd/A 51794-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119854126</v>
+        <v>119854098</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463088</v>
+        <v>462896</v>
       </c>
       <c r="R2" t="n">
-        <v>6718968</v>
+        <v>6718825</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -783,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119854098</v>
+        <v>119854067</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462896</v>
+        <v>462894</v>
       </c>
       <c r="R3" t="n">
-        <v>6718825</v>
+        <v>6718746</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119854075</v>
+        <v>119854126</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,31 +899,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462904</v>
+        <v>463088</v>
       </c>
       <c r="R4" t="n">
-        <v>6718824</v>
+        <v>6718968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119854067</v>
+        <v>119854075</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,30 +1007,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462894</v>
+        <v>462904</v>
       </c>
       <c r="R5" t="n">
-        <v>6718746</v>
+        <v>6718824</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
